--- a/data/gravel/Cannondale Topstone Carbon 2025.xlsx
+++ b/data/gravel/Cannondale Topstone Carbon 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57112D37-937B-6241-88E7-DBB6981E488C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313AA3AC-FED2-5A41-B720-1B762A7AF098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3520" yWindow="2480" windowWidth="25280" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -348,13 +348,16 @@
   </si>
   <si>
     <t>Topstone Carbon</t>
+  </si>
+  <si>
+    <t>https://embed.widencdn.net/img/dorelrl/zum5yy6yo9/1700px@1x/C25_C15145U_Topstone_Crb_LTD_Di2_MGY_PD.webp?color=F8F8F6&amp;q=99</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -379,6 +382,13 @@
       <name val="Futura"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -397,17 +407,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -748,6 +761,11 @@
         <v>93</v>
       </c>
     </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
@@ -2155,6 +2173,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{64357702-5764-AD46-A9D4-087BC044AB56}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data/gravel/Cannondale Topstone Carbon 2025.xlsx
+++ b/data/gravel/Cannondale Topstone Carbon 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313AA3AC-FED2-5A41-B720-1B762A7AF098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF52AF55-6435-8742-9D5A-69C8F7AABD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3520" yWindow="2480" windowWidth="25280" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,12 @@
   </si>
   <si>
     <t>https://embed.widencdn.net/img/dorelrl/zum5yy6yo9/1700px@1x/C25_C15145U_Topstone_Crb_LTD_Di2_MGY_PD.webp?color=F8F8F6&amp;q=99</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Wilton, Connecticut, USA</t>
   </si>
 </sst>
 </file>
@@ -715,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2172,6 +2178,14 @@
         <v>103</v>
       </c>
     </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{64357702-5764-AD46-A9D4-087BC044AB56}"/>

--- a/data/gravel/Cannondale Topstone Carbon 2025.xlsx
+++ b/data/gravel/Cannondale Topstone Carbon 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF52AF55-6435-8742-9D5A-69C8F7AABD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AC42ED-0561-3445-B019-883B86AB6CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3520" yWindow="2480" windowWidth="25280" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,24 @@
   </si>
   <si>
     <t>Wilton, Connecticut, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -721,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2024,165 +2042,195 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53">
-        <v>27.2</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B59">
+        <v>27.2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
-      </c>
-      <c r="B66">
-        <v>1</v>
+        <v>56</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67">
-        <v>3</v>
+        <v>57</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B72">
-        <v>3799</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="B73">
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B78">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>70</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>106</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>107</v>
       </c>
     </row>
